--- a/EMMA_Token_Efficiency_Benchmark.xlsx
+++ b/EMMA_Token_Efficiency_Benchmark.xlsx
@@ -8,20 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keyva\Emma_Docker_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{8E3CD97A-AEEB-43FF-A26E-E063F58FB41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A7A1AA-23F5-4527-A207-0F7D551CE6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark Queries" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Benchmark Queries'!$A$1:$G$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Benchmark Queries'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -137,70 +135,31 @@
     <t>Can you remind me what my core values are?</t>
   </si>
   <si>
-    <t>دسته</t>
-  </si>
-  <si>
-    <t>سوال بازنویسی‌شده</t>
-  </si>
-  <si>
-    <t>هدف ارزیابی (Ground Truth در حافظه)</t>
-  </si>
-  <si>
     <t>What did we talk about regarding my son Kourosh in our first session?</t>
   </si>
   <si>
-    <t>بازیابی اپیزودیک / جلسات (علاقه‌مندی‌های کوروش و نجاری/نقاشی)</t>
-  </si>
-  <si>
-    <t>بازیابی معنایی (core_values در حافظه معنایی)</t>
-  </si>
-  <si>
     <t>What major life goal did I say I’m focusing on regarding Canada?</t>
   </si>
   <si>
-    <t>بازیابی حافظه اپیزودیک/جلسه دوم (مهاجرت و تمرین زبان)</t>
-  </si>
-  <si>
     <t>What did I tell you about my son’s hobbies and technical talents?</t>
   </si>
   <si>
-    <t>بازیابی جزئیات مکالمه جلسه اول (کارهای فنی، کار با چوب و رنگ‌آمیزی)</t>
-  </si>
-  <si>
     <t>How did I say I manage my time between my AI work and my studies?</t>
   </si>
   <si>
-    <t>بازیابی رفتارها و مکالمه (تنظیم ساعات کاری با ساعات مدرسه فرزند)</t>
-  </si>
-  <si>
     <t>What did I mention was making me feel slightly overwhelmed recently?</t>
   </si>
   <si>
-    <t>بازیابی وضعیت احساسی اپیزودیک (تعادل بین ارشد معماری کامپیوتر و والدگری)</t>
-  </si>
-  <si>
     <t>Do you remember what field my Master’s studies are in?</t>
   </si>
   <si>
-    <t>بازیابی واقعیت مشخص از سشن اول (MSc in Computer Architecture)</t>
-  </si>
-  <si>
     <t>What can you tell me about my personality traits based on your analysis?</t>
   </si>
   <si>
-    <t>بازیابی شاخص‌های پنج‌گانه (personality_traits در حافظه معنایی)</t>
-  </si>
-  <si>
     <t>What did we discuss about English vocabulary in our last conversation?</t>
   </si>
   <si>
-    <t>بازیابی جلسه دوم (مترادف‌های کلمه opportunities و تمرین نگارش)</t>
-  </si>
-  <si>
     <t>What are the recurring themes you’ve observed in our past sessions?</t>
-  </si>
-  <si>
-    <t>بازیابی تم‌های تکرارشونده (recurring_themes در حافظه معنایی)</t>
   </si>
 </sst>
 </file>
@@ -684,13 +643,15 @@
       <c r="C2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>121</v>
+      </c>
       <c r="E2" s="5">
         <v>155</v>
       </c>
       <c r="F2" s="6">
         <f t="shared" ref="F2:F31" si="0">IF(E2&gt;0, (E2-D2)/E2*100, 0)</f>
-        <v>100</v>
+        <v>21.935483870967744</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>9</v>
@@ -706,13 +667,15 @@
       <c r="C3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="9">
+        <v>154</v>
+      </c>
       <c r="E3" s="9">
         <v>184</v>
       </c>
       <c r="F3" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>16.304347826086957</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>9</v>
@@ -728,13 +691,15 @@
       <c r="C4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="5">
+        <v>189</v>
+      </c>
       <c r="E4" s="5">
         <v>217</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>12.903225806451612</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>9</v>
@@ -750,13 +715,15 @@
       <c r="C5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="9">
+        <v>230</v>
+      </c>
       <c r="E5" s="9">
         <v>259</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>11.196911196911197</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>9</v>
@@ -772,13 +739,15 @@
       <c r="C6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="5">
+        <v>268</v>
+      </c>
       <c r="E6" s="5">
         <v>305</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>12.131147540983607</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>9</v>
@@ -794,13 +763,15 @@
       <c r="C7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="9">
+        <v>295</v>
+      </c>
       <c r="E7" s="9">
         <v>339</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>12.979351032448378</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -816,13 +787,15 @@
       <c r="C8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="5">
+        <v>483</v>
+      </c>
       <c r="E8" s="5">
         <v>580</v>
       </c>
       <c r="F8" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>16.724137931034484</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>9</v>
@@ -838,13 +811,15 @@
       <c r="C9" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="9">
+        <v>547</v>
+      </c>
       <c r="E9" s="9">
         <v>662</v>
       </c>
       <c r="F9" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>17.371601208459214</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>9</v>
@@ -860,13 +835,15 @@
       <c r="C10" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="5">
+        <v>621</v>
+      </c>
       <c r="E10" s="5">
         <v>754</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>17.639257294429708</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>9</v>
@@ -882,13 +859,15 @@
       <c r="C11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="9">
+        <v>793</v>
+      </c>
       <c r="E11" s="9">
         <v>921</v>
       </c>
       <c r="F11" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>13.897937024972856</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>9</v>
@@ -904,13 +883,15 @@
       <c r="C12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="5">
+        <v>125</v>
+      </c>
       <c r="E12" s="5">
         <v>160</v>
       </c>
       <c r="F12" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>21.875</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>9</v>
@@ -926,13 +907,15 @@
       <c r="C13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9">
+        <v>409</v>
+      </c>
       <c r="E13" s="9">
         <v>517</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>20.889748549323016</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>9</v>
@@ -948,13 +931,15 @@
       <c r="C14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14" s="5">
+        <v>690</v>
+      </c>
       <c r="E14" s="5">
         <v>827</v>
       </c>
       <c r="F14" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>16.565900846432889</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>9</v>
@@ -970,13 +955,15 @@
       <c r="C15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="9"/>
+      <c r="D15" s="9">
+        <v>958</v>
+      </c>
       <c r="E15" s="9">
         <v>1157</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>17.199654278305964</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>9</v>
@@ -992,13 +979,15 @@
       <c r="C16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="5"/>
+      <c r="D16" s="5">
+        <v>1253</v>
+      </c>
       <c r="E16" s="5">
         <v>1516</v>
       </c>
       <c r="F16" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>17.348284960422163</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>9</v>
@@ -1014,13 +1003,15 @@
       <c r="C17" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="9"/>
+      <c r="D17" s="9">
+        <v>1518</v>
+      </c>
       <c r="E17" s="9">
         <v>1869</v>
       </c>
       <c r="F17" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>18.780096308186195</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>9</v>
@@ -1036,13 +1027,15 @@
       <c r="C18" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="5">
+        <v>1813</v>
+      </c>
       <c r="E18" s="5">
         <v>2223</v>
       </c>
       <c r="F18" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>18.443544759334234</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>9</v>
@@ -1058,13 +1051,15 @@
       <c r="C19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="9"/>
+      <c r="D19" s="9">
+        <v>2151</v>
+      </c>
       <c r="E19" s="9">
         <v>2634</v>
       </c>
       <c r="F19" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>18.337129840546698</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>9</v>
@@ -1080,13 +1075,15 @@
       <c r="C20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="5"/>
+      <c r="D20" s="5">
+        <v>2179</v>
+      </c>
       <c r="E20" s="5">
         <v>2613</v>
       </c>
       <c r="F20" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>16.609261385380787</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>9</v>
@@ -1102,13 +1099,15 @@
       <c r="C21" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="D21" s="9">
+        <v>2151</v>
+      </c>
       <c r="E21" s="9">
         <v>2665</v>
       </c>
       <c r="F21" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>19.287054409005627</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>9</v>
@@ -1122,15 +1121,17 @@
         <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="D22" s="5">
+        <v>548</v>
+      </c>
       <c r="E22" s="5">
         <v>547</v>
       </c>
       <c r="F22" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>-0.18281535648994515</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>9</v>
@@ -1146,13 +1147,15 @@
       <c r="C23" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="9">
+        <v>196</v>
+      </c>
       <c r="E23" s="9">
         <v>634</v>
       </c>
       <c r="F23" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>69.085173501577287</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>9</v>
@@ -1166,15 +1169,17 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="D24" s="5">
+        <v>706</v>
+      </c>
       <c r="E24" s="5">
         <v>724</v>
       </c>
       <c r="F24" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>2.4861878453038675</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>9</v>
@@ -1188,15 +1193,17 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="D25" s="9">
+        <v>752</v>
+      </c>
       <c r="E25" s="9">
         <v>792</v>
       </c>
       <c r="F25" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>5.0505050505050502</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>9</v>
@@ -1210,15 +1217,17 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="D26" s="5">
+        <v>804</v>
+      </c>
       <c r="E26" s="5">
         <v>858</v>
       </c>
       <c r="F26" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>6.2937062937062942</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>9</v>
@@ -1232,15 +1241,17 @@
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="D27" s="9">
+        <v>872</v>
+      </c>
       <c r="E27" s="9">
         <v>929</v>
       </c>
       <c r="F27" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>6.1356297093649088</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>9</v>
@@ -1254,15 +1265,17 @@
         <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="D28" s="5">
+        <v>967</v>
+      </c>
       <c r="E28" s="5">
         <v>993</v>
       </c>
       <c r="F28" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>2.6183282980866065</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>9</v>
@@ -1276,15 +1289,17 @@
         <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="9"/>
+        <v>38</v>
+      </c>
+      <c r="D29" s="9">
+        <v>575</v>
+      </c>
       <c r="E29" s="9">
         <v>1051</v>
       </c>
       <c r="F29" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>45.290199809705044</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>9</v>
@@ -1298,15 +1313,17 @@
         <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="5"/>
+        <v>39</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1019</v>
+      </c>
       <c r="E30" s="5">
         <v>1064</v>
       </c>
       <c r="F30" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>4.2293233082706765</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>9</v>
@@ -1320,15 +1337,17 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="9"/>
+        <v>40</v>
+      </c>
+      <c r="D31" s="9">
+        <v>1031</v>
+      </c>
       <c r="E31" s="9">
         <v>1062</v>
       </c>
       <c r="F31" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>2.9190207156308849</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>9</v>
@@ -1351,171 +1370,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD13174-AE12-4C0F-A071-C01B1BACE8A8}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="62.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>